--- a/game49-去掉自动化逻辑/web.xlsx
+++ b/game49-去掉自动化逻辑/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="14280" windowHeight="11730"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="13" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>domain</t>
   </si>
@@ -45,28 +45,10 @@
     <t>json</t>
   </si>
   <si>
-    <t>play.fairylike.site</t>
+    <t>cramdown.site</t>
   </si>
   <si>
     <t>#fac03d</t>
-  </si>
-  <si>
-    <t>sec.fairylike.site</t>
-  </si>
-  <si>
-    <t>#5c4f55</t>
-  </si>
-  <si>
-    <t>play.exonerative.site</t>
-  </si>
-  <si>
-    <t>#aa9649</t>
-  </si>
-  <si>
-    <t>sec.exonerative.site</t>
-  </si>
-  <si>
-    <t>#f53d93</t>
   </si>
   <si>
     <t>color</t>
@@ -112,7 +94,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -166,23 +148,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF018FFB"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF2972F4"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -706,152 +694,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -891,6 +879,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1318,7 +1309,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" ht="16.5" spans="1:5">
       <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
@@ -1334,58 +1325,28 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>8</v>
-      </c>
+      <c r="A3" s="14"/>
+      <c r="B3" s="15"/>
       <c r="C3" s="13"/>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>18</v>
-      </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>10</v>
-      </c>
+      <c r="A4" s="14"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="13"/>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>16</v>
-      </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>12</v>
-      </c>
+      <c r="A5" s="14"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="10"/>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>15</v>
-      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6"/>
-      <c r="B6" s="17"/>
+      <c r="B6" s="18"/>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="10"/>
-      <c r="B7" s="18"/>
+      <c r="B7" s="19"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -1398,6 +1359,9 @@
       <c r="E8" s="10"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="cramdown.site" tooltip="https://dash.cloudflare.com/9c8e1e45e69cebbd9c612503f7f5f227/cramdown.site"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1417,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -1425,46 +1389,46 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="10"/>
